--- a/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>通電導線在磁場中會？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>力</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>受力增大</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>受力</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>受磁力</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>受力方向與什麼有關？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>左手(佛萊明)定則</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>電流方向與磁場平行時</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>電流與磁場方向</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>判斷受力方向可用？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>左手(佛萊明)定則</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>馬達電轉動、發電機動轉電</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>電能轉動能效率高低污染</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電流方向與磁場平行時</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>定則</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>馬達把電能轉成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>受力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>換向器</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>轉動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>馬達利用通電線圈在磁場中？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>換向器</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>部分熱能散失</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>受力轉動</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>改變電流方向受力？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>受力</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>反向</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>部分熱能散失</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>隨電流</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>電風扇靠什麼轉動？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>受力增大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>馬達</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>電動機</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>不通電的導線在磁場受力嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>部分熱能散失</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>不受力</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>需電流</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>馬達把電能轉換成什麼能？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>不受力</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>馬達</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>轉動</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>通電導線放在磁場中會受到？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>力</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>受力</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>電流與磁場方向平行時受力？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>不受力</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>平行</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>馬達持續轉動需要什麼裝置？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>換向器</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不受力</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>換向</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>改變磁場方向受力方向？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>維持原方向</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>改變</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>隨磁場</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>電流磁場受力三者關係？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不受力</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>互相垂直</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>正交</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>馬達是能量從電轉？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>動能</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>換向器</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>受力增大</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>電→動</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>電動車動力來自？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>馬達</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>維持原方向</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>力</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>電能</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>同時反轉電流與磁場受力方向？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>不變</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>馬達</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>力</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>兩次反向</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>洗衣機滾筒轉動靠？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>受力增大</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>部分熱能散失</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>馬達</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>電動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>馬達內使線圈持續轉的裝置是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>力</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>受力增大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>換向器</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>換向</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>電流與磁場垂直時導線受力最？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>改變</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>受力</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>最大</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下2-3 電流在磁場中受力　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>馬達為何需要換向器才能持續轉動？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>電流方向與磁場平行時</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>磁場食指電流中指則拇指為力</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>電能轉動能效率高低污染</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>週期性改變電流方向維持同向轉矩</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>換向</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用左手定則說明受力方向判斷？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>磁場食指電流中指則拇指為力</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>馬達電轉動、發電機動轉電</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>電能轉動能效率高低污染</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>定則</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>馬達與發電機能量轉換方向相反如何區分？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>馬達電轉動、發電機動轉電</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>週期性改變電流方向維持同向轉矩</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>電流方向與磁場平行時</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>馬達電→動、發電機動→電</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>對比</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>何時通電導線在磁場中不受力？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>電能轉動能效率高低污染</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>馬達電轉動、發電機動轉電</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>電流方向與磁場平行時</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>磁場食指電流中指則拇指為力</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>特例</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>電動車以馬達驅動的優點？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>電能轉動能效率高低污染</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>磁場食指電流中指則拇指為力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>左手(佛萊明)定則</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>若同時反轉電流與磁場,轉向如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>維持原方向</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>改變</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>馬達</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>雙反</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>增大電流或磁場對受力影響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>動能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>受力增大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>增強</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>馬達把電能轉動能過程也伴隨？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>不變</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>部分熱能散失</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>馬達</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>效率</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>馬達與發電機能量轉換方向如何？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>馬達電→動、發電機動→電</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>電能轉動能效率高低污染</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>週期性改變電流方向維持同向轉矩</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>馬達電轉動、發電機動轉電</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>互逆</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>電風扇洗衣機的轉動核心元件是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>反向</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>受力轉動</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>馬達</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>互相垂直</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>電動機</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>受磁力</t>
+          <t>受磁力：把有電流通過的導線放進磁場裡，導線會受到一股磁力的作用</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者：導線受力的方向，同時和電流流動的方向、磁場的方向都有關係</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>定則</t>
+          <t>定則：要判斷通電導線受力的方向，可以利用左手(佛萊明)定則來幫忙判斷</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>轉動</t>
+          <t>轉動：馬達運作時，會把輸入的電能轉換成讓機件轉動的動能</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：馬達的原理是讓通電的線圈放在磁場中受力，因而帶動線圈不斷轉動</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>隨電流</t>
+          <t>隨電流：把導線裡電流的方向反過來，導線所受磁力的方向也會跟著反轉</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>電動機</t>
+          <t>電動機：電風扇是靠內部的馬達(電動機)通電後轉動，才能帶動扇葉吹出風</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>需電流</t>
+          <t>需電流：導線如果沒有電流通過，就算放在磁場裡也不會受到磁力作用</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>轉動</t>
+          <t>轉動：馬達運作時會把輸入的電能轉換成帶動裝置轉動的動能</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>受力</t>
+          <t>受力：有電流通過的導線放進磁場裡，會受到一股磁力的作用</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>平行</t>
+          <t>平行：當電流方向和磁場方向剛好平行時，導線反而不會受到磁力作用</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>換向</t>
+          <t>換向：馬達要能持續同方向轉動，需要換向器定時改變線圈裡電流的方向</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>隨磁場</t>
+          <t>隨磁場：把磁場的方向反過來，通電導線所受磁力的方向也會跟著改變</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正交</t>
+          <t>正交：電流方向、磁場方向和導線所受的力，這三者彼此互相垂直</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>電→動</t>
+          <t>電→動：馬達的作用是把電能轉換成動能，帶動裝置轉動起來</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>電能</t>
+          <t>電能：電動車是靠馬達把電池裡的電能轉換成動能，驅動車輪前進</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>兩次反向</t>
+          <t>兩次反向：如果同時把電流方向和磁場方向都反轉，兩次反向互相抵消，受力方向會維持不變</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>電動</t>
+          <t>電動：洗衣機裡的滾筒是靠馬達通電後產生轉動的力量來帶動旋轉</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>換向</t>
+          <t>換向：換向器會定時改變線圈裡電流的方向，讓馬達能持續同方向轉動</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>最大</t>
+          <t>最大：當電流方向和磁場方向互相垂直時，導線所受到的磁力會達到最大</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>換向</t>
+          <t>換向：換向器會定時切換線圈裡電流的方向，讓線圈每次轉半圈後仍受到同方向的力，才能持續轉下去</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>定則</t>
+          <t>定則：使用左手定則時，食指指磁場方向、中指指電流方向，這時拇指所指的方向就是導線受力的方向</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對比</t>
+          <t>對比：馬達是把輸入的電能轉換成動能帶動轉動，發電機則相反，是把轉動的動能轉換成電能</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>特例</t>
+          <t>特例：當導線裡電流的方向和磁場方向剛好互相平行時，導線就不會受到磁力作用</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：馬達把電能轉為動能的過程效率較高，而且行駛時不會像燃油車一樣排放廢氣汙染空氣</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>雙反</t>
+          <t>雙反：電流方向和磁場方向若同時反轉，兩次改變互相抵消，導線受力方向仍會保持原本的方向</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>增強</t>
+          <t>增強：不管是加大通過導線的電流，還是增強周圍的磁場，都會讓導線所受的磁力變得更大</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>效率</t>
+          <t>效率：馬達運轉時線圈和零件之間會有摩擦與電阻，因此有一部分電能會轉成熱能而散失，無法百分之百轉成動能</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>互逆</t>
+          <t>互逆：馬達是把電能轉成動能帶動轉動，發電機則相反，是把動能轉成電能，兩者方向互逆</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>電動機</t>
+          <t>電動機：電風扇和洗衣機裡負責帶動轉動的核心元件都是馬達(電動機)</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下2-3_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>部分熱能散失</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>受力增大</t>
+          <t>換向器</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>受力轉動</t>
+          <t>維持原方向</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>反向</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>換向器</t>
+          <t>改變</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>部分熱能散失</t>
+          <t>大</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>部分熱能散失</t>
+          <t>互相垂直</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>互相垂直</t>
+          <t>維持原方向</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>反向</t>
+          <t>馬達</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>換向器</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>部分熱能散失</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>大</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>大</t>
+          <t>部分熱能散失</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>不變</t>
+          <t>改變</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>改變</t>
+          <t>換向器</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>受力轉動</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>受力</t>
+          <t>動能</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>受力轉動</t>
+          <t>不變</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>動能</t>
+          <t>馬達</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
